--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/dic-2025.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/dic-2025.xlsx
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>26.722</v>
+        <v>1157.21</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>25.86</v>
+        <v>1119.88</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>348.488</v>
+        <v>15091.44</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>14.56</v>
+        <v>630.53</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>13.104</v>
+        <v>567.47</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>197.104</v>
+        <v>8535.68</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>350.52</v>
+        <v>15179.44</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>41.656</v>
+        <v>1803.93</v>
       </c>
     </row>
     <row r="10">
@@ -1053,11 +1053,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>773.9299999999999</v>
+        <v>33515.41</v>
       </c>
     </row>
     <row r="11">
@@ -1114,11 +1114,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>149.352</v>
+        <v>6467.76</v>
       </c>
     </row>
     <row r="12">
@@ -1175,11 +1175,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>215.392</v>
+        <v>9327.65</v>
       </c>
     </row>
     <row r="13">
@@ -1236,11 +1236,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>192.024</v>
+        <v>8315.690000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1297,11 +1297,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>754.888</v>
+        <v>32690.79</v>
       </c>
     </row>
     <row r="15">
@@ -1362,11 +1362,11 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>6949.56192</v>
+        <v>300954.1</v>
       </c>
     </row>
     <row r="16">
@@ -1427,11 +1427,11 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>11418.24</v>
+        <v>494472.34</v>
       </c>
     </row>
     <row r="17">
@@ -1488,11 +1488,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>774.895</v>
+        <v>33557.2</v>
       </c>
     </row>
     <row r="18">
@@ -1549,11 +1549,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1200.912</v>
+        <v>52006.07</v>
       </c>
     </row>
     <row r="19">
@@ -1610,11 +1610,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1200.912</v>
+        <v>52006.07</v>
       </c>
     </row>
     <row r="20">
@@ -1671,11 +1671,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>64.008</v>
+        <v>2771.9</v>
       </c>
     </row>
     <row r="21">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>130917.36</v>
+        <v>5669438.88</v>
       </c>
     </row>
   </sheetData>
